--- a/jpcore-r4/main/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Device.id</t>
@@ -367,7 +367,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Device.meta.versionId</t>
@@ -860,7 +860,7 @@
     <t>Device.status</t>
   </si>
   <si>
-    <t>アクティブ|非アクティブ|エラーに入った|わからない / active | inactive | entered-in-error | unknown</t>
+    <t>アクティブ|非アクティブ|エラー入力|わからない / active | inactive | entered-in-error | unknown</t>
   </si>
   <si>
     <t>デバイスの可用性のステータス。 / Status of the Device availability.</t>

--- a/jpcore-r4/main/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-device.xlsx
@@ -1664,17 +1664,17 @@
   <dimension ref="A1:AM75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.6015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="28.6484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1683,25 +1683,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.56640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="63.0703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.71484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.40234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-device.xlsx
@@ -431,7 +431,7 @@
     <t>Device.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -527,7 +527,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>Device.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DeviceDefinition)
+    <t xml:space="preserve">Reference(DeviceDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>デバイスの可用性ステータス理由。 / The availability status reason of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1079,7 +1079,7 @@
     <t>医療機器を識別するコード。 / Codes to identify medical devices.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-type</t>
+    <t>http://hl7.org/fhir/ValueSet/device-type|4.0.1</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1215,7 +1215,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1275,7 +1275,7 @@
     <t>Device.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1337,7 +1337,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1674,7 +1674,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1689,7 +1689,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.0703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="40.71484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-device.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
